--- a/artfynd/Fröbäckstjärnarna artfynd.xlsx
+++ b/artfynd/Fröbäckstjärnarna artfynd.xlsx
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97023566</v>
+        <v>53489741</v>
       </c>
       <c r="B9" t="n">
-        <v>93235</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,37 +1476,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Staverberget, nordost om, Mpd</t>
+          <t>Sörmarksflon, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497185</v>
+        <v>497226</v>
       </c>
       <c r="R9" t="n">
-        <v>6910786</v>
+        <v>6910362</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1530,12 +1534,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>1997-09-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>1997-09-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,18 +1553,18 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>olikåldrig och gallrad, f.d. brandpräglad tallskog</t>
+          <t>SCA Skogsmark</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Caroline Westerlund</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Tomas Rydkvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1571,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>53489741</v>
+        <v>97023553</v>
       </c>
       <c r="B10" t="n">
-        <v>80432</v>
+        <v>78334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,41 +1586,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sörmarksflon, Mpd</t>
+          <t>Staverberget, nordost om, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497226</v>
+        <v>496777</v>
       </c>
       <c r="R10" t="n">
-        <v>6910362</v>
+        <v>6910438</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1997-09-19</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1997-09-19</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,18 +1659,26 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>SCA Skogsmark</t>
+          <t>olikåldrig tallskog med stor diameterspridning och gamla brandspår</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>1 substratenheter # torraka, 25 cm bred</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Rydkvist</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1681,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97023553</v>
+        <v>53489743</v>
       </c>
       <c r="B11" t="n">
-        <v>78334</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,37 +1700,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Staverberget, nordost om, Mpd</t>
+          <t>Sörmarksflon, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496777</v>
+        <v>497037</v>
       </c>
       <c r="R11" t="n">
-        <v>6910438</v>
+        <v>6910370</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,12 +1758,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>1997-09-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>1997-09-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,26 +1777,18 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>olikåldrig tallskog med stor diameterspridning och gamla brandspår</t>
-        </is>
-      </c>
-      <c r="AN11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>1 substratenheter # torraka, 25 cm bred</t>
+          <t>SCA Skogsmark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Caroline Westerlund</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Tomas Rydkvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1795,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>53489743</v>
+        <v>97023554</v>
       </c>
       <c r="B12" t="n">
-        <v>57953</v>
+        <v>5495</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,41 +1810,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>101410</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sörmarksflon, Mpd</t>
+          <t>Staverberget, nordost om, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497037</v>
+        <v>496753</v>
       </c>
       <c r="R12" t="n">
-        <v>6910370</v>
+        <v>6910455</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1997-09-19</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1997-09-19</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,18 +1883,26 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>SCA Skogsmark</t>
+          <t>olikåldrig tallskog med stor diameterspridning och gamla brandspår</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>1 substratenheter # typiska spår i ca 250-årig tall</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Rydkvist</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1905,48 +1913,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97023554</v>
+        <v>53489740</v>
       </c>
       <c r="B13" t="n">
-        <v>5495</v>
+        <v>57132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Staverberget, nordost om, Mpd</t>
+          <t>Sörmarksflon, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496753</v>
+        <v>497226</v>
       </c>
       <c r="R13" t="n">
-        <v>6910455</v>
+        <v>6910362</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1970,12 +1982,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>1997-09-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>1997-09-19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,26 +2001,18 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>olikåldrig tallskog med stor diameterspridning och gamla brandspår</t>
-        </is>
-      </c>
-      <c r="AN13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>1 substratenheter # typiska spår i ca 250-årig tall</t>
+          <t>SCA Skogsmark</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Caroline Westerlund</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Tomas Rydkvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2019,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97023564</v>
+        <v>97023566</v>
       </c>
       <c r="B14" t="n">
-        <v>5495</v>
+        <v>93235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2034,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101410</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497186</v>
+        <v>497185</v>
       </c>
       <c r="R14" t="n">
-        <v>6910733</v>
+        <v>6910786</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2104,14 +2108,6 @@
       <c r="AI14" t="inlineStr">
         <is>
           <t>olikåldrig och gallrad, f.d. brandpräglad tallskog</t>
-        </is>
-      </c>
-      <c r="AN14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>1 substratenheter # typiska spår i ca 200-årig tall</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2133,52 +2129,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>53489740</v>
+        <v>97023564</v>
       </c>
       <c r="B15" t="n">
-        <v>57132</v>
+        <v>5495</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>101410</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sörmarksflon, Mpd</t>
+          <t>Staverberget, nordost om, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497226</v>
+        <v>497186</v>
       </c>
       <c r="R15" t="n">
-        <v>6910362</v>
+        <v>6910733</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2202,12 +2194,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>1997-09-19</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1997-09-19</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2221,18 +2213,26 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>SCA Skogsmark</t>
+          <t>olikåldrig och gallrad, f.d. brandpräglad tallskog</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>1 substratenheter # typiska spår i ca 200-årig tall</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Rydkvist</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -4354,10 +4354,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118370792</v>
+        <v>104441809</v>
       </c>
       <c r="B35" t="n">
-        <v>80432</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4365,34 +4365,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storkullstjärnen, Storkullstjärnen, Mpd</t>
+          <t>Markslåttjärn, 800 m norr om, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497654</v>
+        <v>497475</v>
       </c>
       <c r="R35" t="n">
-        <v>6910788</v>
+        <v>6911075</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4419,22 +4419,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4445,76 +4435,78 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>lövrik barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>5 substratenheter # grova och höga brandstubbar</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118370567</v>
+        <v>104441808</v>
       </c>
       <c r="B36" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Storkullstjärnen, Storkullstjärnen, Mpd</t>
+          <t>Markslåttjärn, 800 m norr om, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497771</v>
+        <v>497475</v>
       </c>
       <c r="R36" t="n">
-        <v>6910758</v>
+        <v>6911075</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4541,22 +4533,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4567,73 +4549,85 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>lövrik barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>5 substratenheter # grova och höga brandstubbar</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118370370</v>
+        <v>53489732</v>
       </c>
       <c r="B37" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Storkullstjärnen, Storkullstjärnen, Mpd</t>
+          <t>Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497756</v>
+        <v>497527</v>
       </c>
       <c r="R37" t="n">
-        <v>6910746</v>
+        <v>6911176</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4657,22 +4651,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>1997-09-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>1997-09-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4683,70 +4667,70 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>SCA Skogsmark</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Caroline Westerlund</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Tomas Rydkvist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118370412</v>
+        <v>118370792</v>
       </c>
       <c r="B38" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storkullstjärnen, Storkullstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>497790</v>
+        <v>497654</v>
       </c>
       <c r="R38" t="n">
-        <v>6910754</v>
+        <v>6910788</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4815,54 +4799,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118370597</v>
+        <v>118370834</v>
       </c>
       <c r="B39" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Storkullstjärnen, Storkullstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>497757</v>
+        <v>497611</v>
       </c>
       <c r="R39" t="n">
-        <v>6910791</v>
+        <v>6910806</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4931,54 +4906,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118370966</v>
+        <v>118370858</v>
       </c>
       <c r="B40" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Storkullstjärnen, Storkullstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497622</v>
+        <v>497611</v>
       </c>
       <c r="R40" t="n">
-        <v>6910750</v>
+        <v>6910805</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5047,42 +5013,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118371042</v>
+        <v>118370567</v>
       </c>
       <c r="B41" t="n">
-        <v>99118</v>
+        <v>57141</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5091,10 +5063,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497707</v>
+        <v>497771</v>
       </c>
       <c r="R41" t="n">
-        <v>6910701</v>
+        <v>6910758</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5163,7 +5135,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118371070</v>
+        <v>118370370</v>
       </c>
       <c r="B42" t="n">
         <v>99118</v>
@@ -5193,7 +5165,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5207,10 +5179,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497712</v>
+        <v>497756</v>
       </c>
       <c r="R42" t="n">
-        <v>6910702</v>
+        <v>6910746</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5279,45 +5251,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118370526</v>
+        <v>118370412</v>
       </c>
       <c r="B43" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Storkullstjärnen, Storkullstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497767</v>
+        <v>497790</v>
       </c>
       <c r="R43" t="n">
-        <v>6910789</v>
+        <v>6910754</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5386,45 +5367,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118370260</v>
+        <v>118370597</v>
       </c>
       <c r="B44" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Storkullstjärnen, Storkullstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497790</v>
+        <v>497757</v>
       </c>
       <c r="R44" t="n">
-        <v>6910717</v>
+        <v>6910791</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5493,45 +5483,54 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118370942</v>
+        <v>118370818</v>
       </c>
       <c r="B45" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Storkullstjärnen, Storkullstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497608</v>
+        <v>497611</v>
       </c>
       <c r="R45" t="n">
-        <v>6910759</v>
+        <v>6910806</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5600,45 +5599,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>104441809</v>
+        <v>118370966</v>
       </c>
       <c r="B46" t="n">
-        <v>79084</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Markslåttjärn, 800 m norr om, Mpd</t>
+          <t>Storkullstjärnen, Storkullstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497475</v>
+        <v>497622</v>
       </c>
       <c r="R46" t="n">
-        <v>6911075</v>
+        <v>6910750</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5665,12 +5673,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5681,78 +5699,70 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>lövrik barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AN46" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>5 substratenheter # grova och höga brandstubbar</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>104441808</v>
+        <v>118371042</v>
       </c>
       <c r="B47" t="n">
-        <v>79946</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Markslåttjärn, 800 m norr om, Mpd</t>
+          <t>Storkullstjärnen, Storkullstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497475</v>
+        <v>497707</v>
       </c>
       <c r="R47" t="n">
-        <v>6911075</v>
+        <v>6910701</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5779,12 +5789,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5795,85 +5815,73 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>lövrik barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AN47" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>5 substratenheter # grova och höga brandstubbar</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>53489732</v>
+        <v>118371070</v>
       </c>
       <c r="B48" t="n">
-        <v>80432</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fröbäckstjärnarna, Mpd</t>
+          <t>Storkullstjärnen, Storkullstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497527</v>
+        <v>497712</v>
       </c>
       <c r="R48" t="n">
-        <v>6911176</v>
+        <v>6910702</v>
       </c>
       <c r="S48" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5897,12 +5905,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>1997-09-18</t>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>1997-09-18</t>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5913,70 +5931,73 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>SCA Skogsmark</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Tomas Rydkvist</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118370834</v>
+        <v>119290089</v>
       </c>
       <c r="B49" t="n">
-        <v>80432</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Storkullstjärnen, Storkullstjärnen, Mpd</t>
+          <t>Markslåttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497611</v>
+        <v>497562</v>
       </c>
       <c r="R49" t="n">
-        <v>6910806</v>
+        <v>6910845</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6003,22 +6024,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6027,63 +6038,76 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118370858</v>
+        <v>119290119</v>
       </c>
       <c r="B50" t="n">
-        <v>80432</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storkullstjärnen, Storkullstjärnen, Mpd</t>
+          <t>Markslåttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497611</v>
+        <v>497575</v>
       </c>
       <c r="R50" t="n">
-        <v>6910805</v>
+        <v>6910858</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6110,22 +6134,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6134,25 +6148,26 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118370818</v>
+        <v>119290129</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -6182,7 +6197,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6190,16 +6205,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Storkullstjärnen, Storkullstjärnen, Mpd</t>
+          <t>Markslåttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497611</v>
+        <v>497586</v>
       </c>
       <c r="R51" t="n">
-        <v>6910806</v>
+        <v>6910828</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6226,22 +6244,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6250,25 +6258,26 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119290089</v>
+        <v>119290134</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -6298,7 +6307,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6315,10 +6324,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497562</v>
+        <v>497581</v>
       </c>
       <c r="R52" t="n">
-        <v>6910845</v>
+        <v>6910815</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6378,7 +6387,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119290119</v>
+        <v>119290145</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -6408,7 +6417,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6425,10 +6434,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497575</v>
+        <v>497614</v>
       </c>
       <c r="R53" t="n">
-        <v>6910858</v>
+        <v>6910819</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6488,7 +6497,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119290129</v>
+        <v>119290180</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -6518,7 +6527,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6535,10 +6544,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497586</v>
+        <v>497543</v>
       </c>
       <c r="R54" t="n">
-        <v>6910828</v>
+        <v>6911076</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6598,7 +6607,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119290134</v>
+        <v>119290258</v>
       </c>
       <c r="B55" t="n">
         <v>99118</v>
@@ -6628,7 +6637,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6645,10 +6654,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497581</v>
+        <v>497529</v>
       </c>
       <c r="R55" t="n">
-        <v>6910815</v>
+        <v>6911101</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6708,7 +6717,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119290145</v>
+        <v>119290267</v>
       </c>
       <c r="B56" t="n">
         <v>99118</v>
@@ -6755,10 +6764,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497614</v>
+        <v>497507</v>
       </c>
       <c r="R56" t="n">
-        <v>6910819</v>
+        <v>6911090</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6818,7 +6827,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119290180</v>
+        <v>119290273</v>
       </c>
       <c r="B57" t="n">
         <v>99118</v>
@@ -6848,7 +6857,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6865,10 +6874,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497543</v>
+        <v>497504</v>
       </c>
       <c r="R57" t="n">
-        <v>6911076</v>
+        <v>6911082</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6928,7 +6937,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119290258</v>
+        <v>119290287</v>
       </c>
       <c r="B58" t="n">
         <v>99118</v>
@@ -6958,7 +6967,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6975,10 +6984,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497529</v>
+        <v>497485</v>
       </c>
       <c r="R58" t="n">
-        <v>6911101</v>
+        <v>6911090</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7038,57 +7047,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119290267</v>
+        <v>118370526</v>
       </c>
       <c r="B59" t="n">
-        <v>99118</v>
+        <v>97983</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Markslåttjärn, Mpd</t>
+          <t>Storkullstjärnen, Storkullstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497507</v>
+        <v>497767</v>
       </c>
       <c r="R59" t="n">
-        <v>6911090</v>
+        <v>6910789</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7115,12 +7112,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7129,76 +7136,63 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119290273</v>
+        <v>118370260</v>
       </c>
       <c r="B60" t="n">
-        <v>99118</v>
+        <v>79085</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Markslåttjärn, Mpd</t>
+          <t>Storkullstjärnen, Storkullstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497504</v>
+        <v>497790</v>
       </c>
       <c r="R60" t="n">
-        <v>6911082</v>
+        <v>6910717</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7225,12 +7219,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7239,76 +7243,63 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119290287</v>
+        <v>118370942</v>
       </c>
       <c r="B61" t="n">
-        <v>99118</v>
+        <v>79085</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Markslåttjärn, Mpd</t>
+          <t>Storkullstjärnen, Storkullstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497485</v>
+        <v>497608</v>
       </c>
       <c r="R61" t="n">
-        <v>6911090</v>
+        <v>6910759</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7335,12 +7326,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7349,19 +7350,18 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8030,7 +8030,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124256885</v>
+        <v>124255822</v>
       </c>
       <c r="B68" t="n">
         <v>80432</v>
@@ -8065,10 +8065,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>498538</v>
+        <v>498423</v>
       </c>
       <c r="R68" t="n">
-        <v>6909687</v>
+        <v>6910002</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8127,7 +8127,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124255822</v>
+        <v>124256885</v>
       </c>
       <c r="B69" t="n">
         <v>80432</v>
@@ -8162,10 +8162,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>498423</v>
+        <v>498538</v>
       </c>
       <c r="R69" t="n">
-        <v>6910002</v>
+        <v>6909687</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8842,10 +8842,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>104441814</v>
+        <v>104441815</v>
       </c>
       <c r="B76" t="n">
-        <v>79084</v>
+        <v>80432</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8853,21 +8853,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8877,10 +8877,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>498106</v>
+        <v>498042</v>
       </c>
       <c r="R76" t="n">
-        <v>6910724</v>
+        <v>6910648</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8926,12 +8926,15 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>olikåldrig tallnaturskog med brandljudstallar</t>
-        </is>
+          <t>ojämn, skiktad och naturskogsartad barrblandskog</t>
+        </is>
+      </c>
+      <c r="AN76" t="n">
+        <v>5</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>gammal torraka med brandspår</t>
+          <t>5 substratenheter # äldre asp och rönn</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8953,32 +8956,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>104441812</v>
+        <v>104441817</v>
       </c>
       <c r="B77" t="n">
-        <v>79946</v>
+        <v>92183</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8988,10 +8991,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>498106</v>
+        <v>498187</v>
       </c>
       <c r="R77" t="n">
-        <v>6910724</v>
+        <v>6910801</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9037,12 +9040,15 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>olikåldrig tallnaturskog med brandljudstallar</t>
-        </is>
+          <t>blockhav i ljus olikåldrig tallnaturskog med brandljudstallar</t>
+        </is>
+      </c>
+      <c r="AN77" t="n">
+        <v>1</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>gammal torraka med brandspår</t>
+          <t>1 substratenheter # gammal klen och hård tallåga</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9064,10 +9070,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>104441815</v>
+        <v>104441816</v>
       </c>
       <c r="B78" t="n">
-        <v>80432</v>
+        <v>91831</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9075,21 +9081,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>3242</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9099,10 +9105,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>498042</v>
+        <v>497979</v>
       </c>
       <c r="R78" t="n">
-        <v>6910648</v>
+        <v>6910818</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9148,15 +9154,15 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>ojämn, skiktad och naturskogsartad barrblandskog</t>
+          <t>blockfält i ljus olikåldrig tallnaturskog med brandljudstallar</t>
         </is>
       </c>
       <c r="AN78" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>5 substratenheter # äldre asp och rönn</t>
+          <t>1 substratenheter # gammal klen och hård tallåga</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9178,32 +9184,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>104441811</v>
+        <v>104441814</v>
       </c>
       <c r="B79" t="n">
-        <v>99118</v>
+        <v>79084</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9213,10 +9219,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497977</v>
+        <v>498106</v>
       </c>
       <c r="R79" t="n">
-        <v>6910746</v>
+        <v>6910724</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9262,7 +9268,12 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>naturskogsartad barrblandskog med mkt självgallring</t>
+          <t>olikåldrig tallnaturskog med brandljudstallar</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>gammal torraka med brandspår</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9284,49 +9295,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>103456749</v>
+        <v>104441812</v>
       </c>
       <c r="B80" t="n">
-        <v>106244</v>
+        <v>79946</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Övre Butjärn, NV om, Mpd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>497950</v>
+        <v>498106</v>
       </c>
       <c r="R80" t="n">
-        <v>6910759</v>
+        <v>6910724</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9361,11 +9368,6 @@
           <t>2022-06-30</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>100 plantor med 40 blomstänglar</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9377,7 +9379,12 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>tät, drygt 100-årig barrnaturskog på frisk, väldränerad mark</t>
+          <t>olikåldrig tallnaturskog med brandljudstallar</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>gammal torraka med brandspår</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9391,36 +9398,40 @@
           <t>Magnus Andersson</t>
         </is>
       </c>
-      <c r="AY80" t="inlineStr"/>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>104441813</v>
+        <v>104441811</v>
       </c>
       <c r="B81" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9430,10 +9441,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>498106</v>
+        <v>497977</v>
       </c>
       <c r="R81" t="n">
-        <v>6910724</v>
+        <v>6910746</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9479,12 +9490,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>olikåldrig tallnaturskog med brandljudstallar</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>gammal torraka med brandspår</t>
+          <t>naturskogsartad barrblandskog med mkt självgallring</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9506,45 +9512,49 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>104441818</v>
+        <v>103456749</v>
       </c>
       <c r="B82" t="n">
-        <v>79085</v>
+        <v>106244</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>221144</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Övre Butjärn, NV om, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>498211</v>
+        <v>497950</v>
       </c>
       <c r="R82" t="n">
-        <v>6910796</v>
+        <v>6910759</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9579,6 +9589,11 @@
           <t>2022-06-30</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>100 plantor med 40 blomstänglar</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9590,15 +9605,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>ljus olikåldrig tallnaturskog med brandljudstallar</t>
-        </is>
-      </c>
-      <c r="AN82" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>3 substratenheter # gamla tallhögstubbar</t>
+          <t>tät, drygt 100-årig barrnaturskog på frisk, väldränerad mark</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9612,18 +9619,14 @@
           <t>Magnus Andersson</t>
         </is>
       </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>104441819</v>
+        <v>104441813</v>
       </c>
       <c r="B83" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9631,21 +9634,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9655,10 +9658,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>498211</v>
+        <v>498106</v>
       </c>
       <c r="R83" t="n">
-        <v>6910796</v>
+        <v>6910724</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9704,15 +9707,12 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>ljus olikåldrig tallnaturskog med brandljudstallar</t>
-        </is>
-      </c>
-      <c r="AN83" t="n">
-        <v>3</v>
+          <t>olikåldrig tallnaturskog med brandljudstallar</t>
+        </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>3 substratenheter # gamla tallhögstubbar</t>
+          <t>gammal torraka med brandspår</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9734,32 +9734,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>104441817</v>
+        <v>104441818</v>
       </c>
       <c r="B84" t="n">
-        <v>92183</v>
+        <v>79085</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9769,10 +9769,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>498187</v>
+        <v>498211</v>
       </c>
       <c r="R84" t="n">
-        <v>6910801</v>
+        <v>6910796</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9818,15 +9818,15 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>blockhav i ljus olikåldrig tallnaturskog med brandljudstallar</t>
+          <t>ljus olikåldrig tallnaturskog med brandljudstallar</t>
         </is>
       </c>
       <c r="AN84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal klen och hård tallåga</t>
+          <t>3 substratenheter # gamla tallhögstubbar</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9848,10 +9848,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>104441816</v>
+        <v>104441819</v>
       </c>
       <c r="B85" t="n">
-        <v>91831</v>
+        <v>79917</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9859,21 +9859,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3242</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497979</v>
+        <v>498211</v>
       </c>
       <c r="R85" t="n">
-        <v>6910818</v>
+        <v>6910796</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9932,15 +9932,15 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>blockfält i ljus olikåldrig tallnaturskog med brandljudstallar</t>
+          <t>ljus olikåldrig tallnaturskog med brandljudstallar</t>
         </is>
       </c>
       <c r="AN85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal klen och hård tallåga</t>
+          <t>3 substratenheter # gamla tallhögstubbar</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9962,32 +9962,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122817760</v>
+        <v>122817347</v>
       </c>
       <c r="B86" t="n">
-        <v>79085</v>
+        <v>79327</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9997,10 +9997,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>498475</v>
+        <v>498508</v>
       </c>
       <c r="R86" t="n">
-        <v>6911237</v>
+        <v>6911438</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10069,45 +10069,50 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122817347</v>
+        <v>122817660</v>
       </c>
       <c r="B87" t="n">
-        <v>79327</v>
+        <v>57141</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>498508</v>
+        <v>498511</v>
       </c>
       <c r="R87" t="n">
-        <v>6911438</v>
+        <v>6911287</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10139,7 +10144,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10149,7 +10154,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10176,50 +10181,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122817660</v>
+        <v>122816792</v>
       </c>
       <c r="B88" t="n">
-        <v>57141</v>
+        <v>79085</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Fröbäckstjärnarna, Fröbäckstjärnarna, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>498511</v>
+        <v>498415</v>
       </c>
       <c r="R88" t="n">
-        <v>6911287</v>
+        <v>6911388</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10251,7 +10251,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10288,7 +10288,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122816792</v>
+        <v>122816814</v>
       </c>
       <c r="B89" t="n">
         <v>79085</v>
@@ -10323,10 +10323,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>498415</v>
+        <v>498410</v>
       </c>
       <c r="R89" t="n">
-        <v>6911388</v>
+        <v>6911399</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10395,7 +10395,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122816814</v>
+        <v>122817760</v>
       </c>
       <c r="B90" t="n">
         <v>79085</v>
@@ -10430,10 +10430,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>498410</v>
+        <v>498475</v>
       </c>
       <c r="R90" t="n">
-        <v>6911399</v>
+        <v>6911237</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10935,32 +10935,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117700215</v>
+        <v>117700209</v>
       </c>
       <c r="B95" t="n">
-        <v>79917</v>
+        <v>92183</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10970,10 +10970,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>498383</v>
+        <v>498510</v>
       </c>
       <c r="R95" t="n">
-        <v>6912493</v>
+        <v>6912782</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11047,32 +11047,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>117700211</v>
+        <v>117700208</v>
       </c>
       <c r="B96" t="n">
-        <v>97358</v>
+        <v>92083</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>53</v>
+        <v>1503</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11082,10 +11082,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>498378</v>
+        <v>498510</v>
       </c>
       <c r="R96" t="n">
-        <v>6912879</v>
+        <v>6912781</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11128,6 +11128,21 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11144,32 +11159,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>117700209</v>
+        <v>117700210</v>
       </c>
       <c r="B97" t="n">
-        <v>92183</v>
+        <v>79084</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11179,10 +11194,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>498510</v>
+        <v>498436</v>
       </c>
       <c r="R97" t="n">
-        <v>6912782</v>
+        <v>6912848</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11256,32 +11271,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>117700208</v>
+        <v>117700214</v>
       </c>
       <c r="B98" t="n">
-        <v>92083</v>
+        <v>79946</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11291,10 +11306,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>498510</v>
+        <v>498261</v>
       </c>
       <c r="R98" t="n">
-        <v>6912781</v>
+        <v>6912642</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11368,10 +11383,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>117700210</v>
+        <v>124259441</v>
       </c>
       <c r="B99" t="n">
-        <v>79084</v>
+        <v>57953</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11379,37 +11394,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Fröbäckstjärnarna, Enstern, Ånge, Mpd</t>
+          <t>Fröberget  Haverö, Fröberget  Haverö, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>498436</v>
+        <v>498128</v>
       </c>
       <c r="R99" t="n">
-        <v>6912848</v>
+        <v>6912631</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11433,12 +11453,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11449,41 +11469,26 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>117700214</v>
+        <v>117700213</v>
       </c>
       <c r="B100" t="n">
-        <v>79946</v>
+        <v>79085</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11491,21 +11496,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11515,10 +11520,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>498261</v>
+        <v>498245</v>
       </c>
       <c r="R100" t="n">
-        <v>6912642</v>
+        <v>6912776</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11592,10 +11597,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>117700212</v>
+        <v>117700217</v>
       </c>
       <c r="B101" t="n">
-        <v>80432</v>
+        <v>79085</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11603,21 +11608,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11627,10 +11632,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>498348</v>
+        <v>498517</v>
       </c>
       <c r="R101" t="n">
-        <v>6912871</v>
+        <v>6912611</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11673,6 +11678,21 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11689,10 +11709,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124259441</v>
+        <v>117700215</v>
       </c>
       <c r="B102" t="n">
-        <v>57953</v>
+        <v>79917</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11700,42 +11720,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Fröberget  Haverö, Fröberget  Haverö, Mpd</t>
+          <t>Fröbäckstjärnarna, Enstern, Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>498128</v>
+        <v>498383</v>
       </c>
       <c r="R102" t="n">
-        <v>6912631</v>
+        <v>6912493</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11759,12 +11774,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11775,26 +11790,41 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>117700213</v>
+        <v>117700211</v>
       </c>
       <c r="B103" t="n">
-        <v>79085</v>
+        <v>97358</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11802,21 +11832,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11826,10 +11856,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>498245</v>
+        <v>498378</v>
       </c>
       <c r="R103" t="n">
-        <v>6912776</v>
+        <v>6912879</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11872,21 +11902,6 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11903,10 +11918,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>117700217</v>
+        <v>117700212</v>
       </c>
       <c r="B104" t="n">
-        <v>79085</v>
+        <v>80432</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11914,21 +11929,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11938,10 +11953,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>498517</v>
+        <v>498348</v>
       </c>
       <c r="R104" t="n">
-        <v>6912611</v>
+        <v>6912871</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11984,21 +11999,6 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -13632,7 +13632,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125289603</v>
+        <v>125287860</v>
       </c>
       <c r="B120" t="n">
         <v>99118</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J120" t="inlineStr"/>
@@ -13675,10 +13675,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>498908</v>
+        <v>498949</v>
       </c>
       <c r="R120" t="n">
-        <v>6908972</v>
+        <v>6909018</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13738,7 +13738,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125289613</v>
+        <v>125288078</v>
       </c>
       <c r="B121" t="n">
         <v>99118</v>
@@ -13768,7 +13768,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -13781,10 +13781,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>498919</v>
+        <v>498859</v>
       </c>
       <c r="R121" t="n">
-        <v>6908969</v>
+        <v>6909038</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13844,7 +13844,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125289622</v>
+        <v>125288082</v>
       </c>
       <c r="B122" t="n">
         <v>99118</v>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J122" t="inlineStr"/>
@@ -13887,10 +13887,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>498930</v>
+        <v>498870</v>
       </c>
       <c r="R122" t="n">
-        <v>6908974</v>
+        <v>6909031</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13950,7 +13950,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125289631</v>
+        <v>125289603</v>
       </c>
       <c r="B123" t="n">
         <v>99118</v>
@@ -13993,10 +13993,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>498932</v>
+        <v>498908</v>
       </c>
       <c r="R123" t="n">
-        <v>6908965</v>
+        <v>6908972</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14056,7 +14056,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125289641</v>
+        <v>125289613</v>
       </c>
       <c r="B124" t="n">
         <v>99118</v>
@@ -14086,7 +14086,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -14099,10 +14099,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>498943</v>
+        <v>498919</v>
       </c>
       <c r="R124" t="n">
-        <v>6908959</v>
+        <v>6908969</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14162,7 +14162,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125289683</v>
+        <v>125289622</v>
       </c>
       <c r="B125" t="n">
         <v>99118</v>
@@ -14192,7 +14192,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -14205,10 +14205,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>498955</v>
+        <v>498930</v>
       </c>
       <c r="R125" t="n">
-        <v>6908949</v>
+        <v>6908974</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14268,7 +14268,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125292788</v>
+        <v>125289631</v>
       </c>
       <c r="B126" t="n">
         <v>99118</v>
@@ -14311,10 +14311,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>498957</v>
+        <v>498932</v>
       </c>
       <c r="R126" t="n">
-        <v>6908943</v>
+        <v>6908965</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14374,7 +14374,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125292807</v>
+        <v>125289641</v>
       </c>
       <c r="B127" t="n">
         <v>99118</v>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -14417,10 +14417,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>498966</v>
+        <v>498943</v>
       </c>
       <c r="R127" t="n">
-        <v>6908931</v>
+        <v>6908959</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14480,7 +14480,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125292842</v>
+        <v>125289683</v>
       </c>
       <c r="B128" t="n">
         <v>99118</v>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J128" t="inlineStr"/>
@@ -14523,10 +14523,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>498969</v>
+        <v>498955</v>
       </c>
       <c r="R128" t="n">
-        <v>6908929</v>
+        <v>6908949</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14586,7 +14586,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125293095</v>
+        <v>125292788</v>
       </c>
       <c r="B129" t="n">
         <v>99118</v>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -14629,10 +14629,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>498977</v>
+        <v>498957</v>
       </c>
       <c r="R129" t="n">
-        <v>6908914</v>
+        <v>6908943</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -14692,7 +14692,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125293104</v>
+        <v>125292807</v>
       </c>
       <c r="B130" t="n">
         <v>99118</v>
@@ -14722,7 +14722,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -14735,10 +14735,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>498981</v>
+        <v>498966</v>
       </c>
       <c r="R130" t="n">
-        <v>6908909</v>
+        <v>6908931</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -14798,7 +14798,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125293122</v>
+        <v>125292842</v>
       </c>
       <c r="B131" t="n">
         <v>99118</v>
@@ -14828,7 +14828,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -14841,10 +14841,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>498995</v>
+        <v>498969</v>
       </c>
       <c r="R131" t="n">
-        <v>6908908</v>
+        <v>6908929</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -14904,7 +14904,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125293145</v>
+        <v>125293095</v>
       </c>
       <c r="B132" t="n">
         <v>99118</v>
@@ -14934,7 +14934,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -14947,10 +14947,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>499002</v>
+        <v>498977</v>
       </c>
       <c r="R132" t="n">
-        <v>6908900</v>
+        <v>6908914</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -15010,7 +15010,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125293162</v>
+        <v>125293104</v>
       </c>
       <c r="B133" t="n">
         <v>99118</v>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J133" t="inlineStr"/>
@@ -15053,10 +15053,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>499008</v>
+        <v>498981</v>
       </c>
       <c r="R133" t="n">
-        <v>6908894</v>
+        <v>6908909</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -15116,7 +15116,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125293175</v>
+        <v>125293122</v>
       </c>
       <c r="B134" t="n">
         <v>99118</v>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -15159,10 +15159,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>499021</v>
+        <v>498995</v>
       </c>
       <c r="R134" t="n">
-        <v>6908891</v>
+        <v>6908908</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -15222,7 +15222,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125293196</v>
+        <v>125293145</v>
       </c>
       <c r="B135" t="n">
         <v>99118</v>
@@ -15265,10 +15265,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>499049</v>
+        <v>499002</v>
       </c>
       <c r="R135" t="n">
-        <v>6908888</v>
+        <v>6908900</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -15328,7 +15328,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125293266</v>
+        <v>125293162</v>
       </c>
       <c r="B136" t="n">
         <v>99118</v>
@@ -15358,7 +15358,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J136" t="inlineStr"/>
@@ -15371,10 +15371,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>499054</v>
+        <v>499008</v>
       </c>
       <c r="R136" t="n">
-        <v>6908878</v>
+        <v>6908894</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -15434,7 +15434,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125293276</v>
+        <v>125293175</v>
       </c>
       <c r="B137" t="n">
         <v>99118</v>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J137" t="inlineStr"/>
@@ -15477,10 +15477,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>499066</v>
+        <v>499021</v>
       </c>
       <c r="R137" t="n">
-        <v>6908879</v>
+        <v>6908891</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -15540,7 +15540,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125293329</v>
+        <v>125293196</v>
       </c>
       <c r="B138" t="n">
         <v>99118</v>
@@ -15570,7 +15570,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J138" t="inlineStr"/>
@@ -15583,10 +15583,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>499069</v>
+        <v>499049</v>
       </c>
       <c r="R138" t="n">
-        <v>6908868</v>
+        <v>6908888</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -15646,7 +15646,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>96470660</v>
+        <v>125293266</v>
       </c>
       <c r="B139" t="n">
         <v>99118</v>
@@ -15676,29 +15676,26 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Ånge, Mpd</t>
+          <t>Fluganvägen, Mpd</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>498944</v>
+        <v>499054</v>
       </c>
       <c r="R139" t="n">
-        <v>6909094</v>
+        <v>6908878</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15722,12 +15719,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15736,25 +15733,26 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>96470700</v>
+        <v>125293276</v>
       </c>
       <c r="B140" t="n">
         <v>99118</v>
@@ -15784,29 +15782,26 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Ånge, Mpd</t>
+          <t>Fluganvägen, Mpd</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>498950</v>
+        <v>499066</v>
       </c>
       <c r="R140" t="n">
-        <v>6909135</v>
+        <v>6908879</v>
       </c>
       <c r="S140" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15830,12 +15825,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15844,25 +15839,26 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>96470811</v>
+        <v>125293329</v>
       </c>
       <c r="B141" t="n">
         <v>99118</v>
@@ -15892,29 +15888,26 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Ånge, Mpd</t>
+          <t>Fluganvägen, Mpd</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>498876</v>
+        <v>499069</v>
       </c>
       <c r="R141" t="n">
-        <v>6909123</v>
+        <v>6908868</v>
       </c>
       <c r="S141" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15938,12 +15931,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15952,25 +15945,26 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>96470895</v>
+        <v>96470660</v>
       </c>
       <c r="B142" t="n">
         <v>99118</v>
@@ -16016,10 +16010,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>498823</v>
+        <v>498944</v>
       </c>
       <c r="R142" t="n">
-        <v>6909121</v>
+        <v>6909094</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -16078,7 +16072,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125287860</v>
+        <v>96470700</v>
       </c>
       <c r="B143" t="n">
         <v>99118</v>
@@ -16108,26 +16102,29 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Fluganvägen, Mpd</t>
+          <t>Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>498949</v>
+        <v>498950</v>
       </c>
       <c r="R143" t="n">
-        <v>6909018</v>
+        <v>6909135</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16151,12 +16148,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16165,26 +16162,25 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125287871</v>
+        <v>96470811</v>
       </c>
       <c r="B144" t="n">
         <v>99118</v>
@@ -16214,26 +16210,29 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Fluganvägen, Mpd</t>
+          <t>Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>498917</v>
+        <v>498876</v>
       </c>
       <c r="R144" t="n">
-        <v>6909056</v>
+        <v>6909123</v>
       </c>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16257,12 +16256,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16271,26 +16270,25 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125287884</v>
+        <v>96470895</v>
       </c>
       <c r="B145" t="n">
         <v>99118</v>
@@ -16320,26 +16318,29 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Fluganvägen, Mpd</t>
+          <t>Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>498917</v>
+        <v>498823</v>
       </c>
       <c r="R145" t="n">
-        <v>6909071</v>
+        <v>6909121</v>
       </c>
       <c r="S145" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16363,12 +16364,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16377,26 +16378,25 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125287903</v>
+        <v>125287871</v>
       </c>
       <c r="B146" t="n">
         <v>99118</v>
@@ -16426,7 +16426,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J146" t="inlineStr"/>
@@ -16439,10 +16439,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>498951</v>
+        <v>498917</v>
       </c>
       <c r="R146" t="n">
-        <v>6909091</v>
+        <v>6909056</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -16502,7 +16502,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125287937</v>
+        <v>125287884</v>
       </c>
       <c r="B147" t="n">
         <v>99118</v>
@@ -16532,7 +16532,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J147" t="inlineStr"/>
@@ -16545,10 +16545,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>498902</v>
+        <v>498917</v>
       </c>
       <c r="R147" t="n">
-        <v>6909119</v>
+        <v>6909071</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>
@@ -16608,7 +16608,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125287953</v>
+        <v>125287903</v>
       </c>
       <c r="B148" t="n">
         <v>99118</v>
@@ -16638,7 +16638,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J148" t="inlineStr"/>
@@ -16651,10 +16651,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>498900</v>
+        <v>498951</v>
       </c>
       <c r="R148" t="n">
-        <v>6909123</v>
+        <v>6909091</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -16714,7 +16714,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125287997</v>
+        <v>125287937</v>
       </c>
       <c r="B149" t="n">
         <v>99118</v>
@@ -16744,7 +16744,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J149" t="inlineStr"/>
@@ -16757,10 +16757,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>498896</v>
+        <v>498902</v>
       </c>
       <c r="R149" t="n">
-        <v>6909135</v>
+        <v>6909119</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -16820,7 +16820,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125288007</v>
+        <v>125287953</v>
       </c>
       <c r="B150" t="n">
         <v>99118</v>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J150" t="inlineStr"/>
@@ -16863,10 +16863,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>498895</v>
+        <v>498900</v>
       </c>
       <c r="R150" t="n">
-        <v>6909147</v>
+        <v>6909123</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -16926,7 +16926,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125288017</v>
+        <v>125287997</v>
       </c>
       <c r="B151" t="n">
         <v>99118</v>
@@ -16969,10 +16969,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>498891</v>
+        <v>498896</v>
       </c>
       <c r="R151" t="n">
-        <v>6909159</v>
+        <v>6909135</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -17032,7 +17032,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125288024</v>
+        <v>125288007</v>
       </c>
       <c r="B152" t="n">
         <v>99118</v>
@@ -17062,7 +17062,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J152" t="inlineStr"/>
@@ -17075,10 +17075,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>498876</v>
+        <v>498895</v>
       </c>
       <c r="R152" t="n">
-        <v>6909174</v>
+        <v>6909147</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -17138,7 +17138,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125288035</v>
+        <v>125288017</v>
       </c>
       <c r="B153" t="n">
         <v>99118</v>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J153" t="inlineStr"/>
@@ -17181,10 +17181,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>498877</v>
+        <v>498891</v>
       </c>
       <c r="R153" t="n">
-        <v>6909184</v>
+        <v>6909159</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -17244,7 +17244,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125288041</v>
+        <v>125288024</v>
       </c>
       <c r="B154" t="n">
         <v>99118</v>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J154" t="inlineStr"/>
@@ -17287,10 +17287,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>498866</v>
+        <v>498876</v>
       </c>
       <c r="R154" t="n">
-        <v>6909197</v>
+        <v>6909174</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -17350,7 +17350,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125288054</v>
+        <v>125288035</v>
       </c>
       <c r="B155" t="n">
         <v>99118</v>
@@ -17380,7 +17380,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J155" t="inlineStr"/>
@@ -17393,10 +17393,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>498759</v>
+        <v>498877</v>
       </c>
       <c r="R155" t="n">
-        <v>6909086</v>
+        <v>6909184</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -17456,7 +17456,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125288065</v>
+        <v>125288041</v>
       </c>
       <c r="B156" t="n">
         <v>99118</v>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J156" t="inlineStr"/>
@@ -17499,10 +17499,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>498797</v>
+        <v>498866</v>
       </c>
       <c r="R156" t="n">
-        <v>6909081</v>
+        <v>6909197</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -17562,7 +17562,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125288078</v>
+        <v>125288054</v>
       </c>
       <c r="B157" t="n">
         <v>99118</v>
@@ -17592,7 +17592,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J157" t="inlineStr"/>
@@ -17605,10 +17605,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>498859</v>
+        <v>498759</v>
       </c>
       <c r="R157" t="n">
-        <v>6909038</v>
+        <v>6909086</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -17668,7 +17668,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125288082</v>
+        <v>125288065</v>
       </c>
       <c r="B158" t="n">
         <v>99118</v>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J158" t="inlineStr"/>
@@ -17711,10 +17711,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>498870</v>
+        <v>498797</v>
       </c>
       <c r="R158" t="n">
-        <v>6909031</v>
+        <v>6909081</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -19576,49 +19576,56 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>104453052</v>
+        <v>125293862</v>
       </c>
       <c r="B176" t="n">
-        <v>80298</v>
+        <v>99118</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>388</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Märrviksbodarna, Mpd</t>
+          <t>Fluganvägen, Mpd</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>498847</v>
+        <v>499027</v>
       </c>
       <c r="R176" t="n">
-        <v>6909703</v>
+        <v>6909502</v>
       </c>
       <c r="S176" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19642,22 +19649,12 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>10:07</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>10:07</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19666,67 +19663,75 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>104453043</v>
+        <v>125293887</v>
       </c>
       <c r="B177" t="n">
-        <v>80336</v>
+        <v>99118</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Märrviksbodarna, Mpd</t>
+          <t>Fluganvägen, Mpd</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>498809</v>
+        <v>499109</v>
       </c>
       <c r="R177" t="n">
-        <v>6909692</v>
+        <v>6909525</v>
       </c>
       <c r="S177" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -19750,22 +19755,12 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19774,63 +19769,72 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
+      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>124258267</v>
+        <v>125293903</v>
       </c>
       <c r="B178" t="n">
-        <v>80432</v>
+        <v>99118</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Fluganvägen, Mpd</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>498730</v>
+        <v>499115</v>
       </c>
       <c r="R178" t="n">
-        <v>6909760</v>
+        <v>6909539</v>
       </c>
       <c r="S178" t="n">
         <v>5</v>
@@ -19857,12 +19861,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19871,81 +19875,75 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>96765221</v>
+        <v>125293928</v>
       </c>
       <c r="B179" t="n">
-        <v>57141</v>
+        <v>99118</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M179" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Ånge, Mpd</t>
+          <t>Fluganvägen, Mpd</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>499049</v>
+        <v>499111</v>
       </c>
       <c r="R179" t="n">
-        <v>6909619</v>
+        <v>6909539</v>
       </c>
       <c r="S179" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19969,12 +19967,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19983,73 +19981,72 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>124258047</v>
+        <v>125293957</v>
       </c>
       <c r="B180" t="n">
-        <v>58114</v>
+        <v>99118</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Fluganvägen, Mpd</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>498617</v>
+        <v>499139</v>
       </c>
       <c r="R180" t="n">
-        <v>6909667</v>
+        <v>6909550</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -20076,12 +20073,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20090,25 +20087,26 @@
       <c r="AE180" t="b">
         <v>0</v>
       </c>
+      <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="b">
         <v>0</v>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>124257002</v>
+        <v>125294007</v>
       </c>
       <c r="B181" t="n">
         <v>99118</v>
@@ -20138,24 +20136,23 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Fluganvägen, Mpd</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>498588</v>
+        <v>499134</v>
       </c>
       <c r="R181" t="n">
-        <v>6909664</v>
+        <v>6909553</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -20182,12 +20179,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20196,25 +20193,26 @@
       <c r="AE181" t="b">
         <v>0</v>
       </c>
+      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>124257030</v>
+        <v>125294028</v>
       </c>
       <c r="B182" t="n">
         <v>99118</v>
@@ -20244,24 +20242,23 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Fluganvägen, Mpd</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>498590</v>
+        <v>499096</v>
       </c>
       <c r="R182" t="n">
-        <v>6909676</v>
+        <v>6909543</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -20288,12 +20285,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20302,25 +20299,26 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
+      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>124257082</v>
+        <v>125294048</v>
       </c>
       <c r="B183" t="n">
         <v>99118</v>
@@ -20350,24 +20348,23 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
+          <t>Fluganvägen, Mpd</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>498617</v>
+        <v>499093</v>
       </c>
       <c r="R183" t="n">
-        <v>6909667</v>
+        <v>6909546</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -20394,12 +20391,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20408,25 +20405,26 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
+      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>125293862</v>
+        <v>125294065</v>
       </c>
       <c r="B184" t="n">
         <v>99118</v>
@@ -20456,7 +20454,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
@@ -20469,10 +20467,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>499027</v>
+        <v>499078</v>
       </c>
       <c r="R184" t="n">
-        <v>6909502</v>
+        <v>6909561</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -20532,7 +20530,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>125293887</v>
+        <v>125294080</v>
       </c>
       <c r="B185" t="n">
         <v>99118</v>
@@ -20562,7 +20560,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J185" t="inlineStr"/>
@@ -20575,10 +20573,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>499109</v>
+        <v>499069</v>
       </c>
       <c r="R185" t="n">
-        <v>6909525</v>
+        <v>6909556</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -20638,7 +20636,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125293903</v>
+        <v>125294113</v>
       </c>
       <c r="B186" t="n">
         <v>99118</v>
@@ -20668,7 +20666,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
@@ -20681,10 +20679,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>499115</v>
+        <v>499050</v>
       </c>
       <c r="R186" t="n">
-        <v>6909539</v>
+        <v>6909565</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -20744,7 +20742,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125293928</v>
+        <v>125294124</v>
       </c>
       <c r="B187" t="n">
         <v>99118</v>
@@ -20774,7 +20772,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
@@ -20787,10 +20785,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>499111</v>
+        <v>499054</v>
       </c>
       <c r="R187" t="n">
-        <v>6909539</v>
+        <v>6909570</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -20850,56 +20848,49 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125293957</v>
+        <v>104453052</v>
       </c>
       <c r="B188" t="n">
-        <v>99118</v>
+        <v>80298</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr"/>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Fluganvägen, Mpd</t>
+          <t>Märrviksbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>499139</v>
+        <v>498847</v>
       </c>
       <c r="R188" t="n">
-        <v>6909550</v>
+        <v>6909703</v>
       </c>
       <c r="S188" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -20923,12 +20914,22 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2022-11-03</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2022-11-03</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20937,75 +20938,67 @@
       <c r="AE188" t="b">
         <v>0</v>
       </c>
-      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125294007</v>
+        <v>104453043</v>
       </c>
       <c r="B189" t="n">
-        <v>99118</v>
+        <v>80336</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Fluganvägen, Mpd</t>
+          <t>Märrviksbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>499134</v>
+        <v>498809</v>
       </c>
       <c r="R189" t="n">
-        <v>6909553</v>
+        <v>6909692</v>
       </c>
       <c r="S189" t="n">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -21029,12 +21022,22 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2022-11-03</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2022-11-03</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21043,72 +21046,63 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
-      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125294028</v>
+        <v>124258267</v>
       </c>
       <c r="B190" t="n">
-        <v>99118</v>
+        <v>80432</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Fluganvägen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>499096</v>
+        <v>498730</v>
       </c>
       <c r="R190" t="n">
-        <v>6909543</v>
+        <v>6909760</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -21135,12 +21129,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21149,75 +21143,66 @@
       <c r="AE190" t="b">
         <v>0</v>
       </c>
-      <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="b">
         <v>0</v>
       </c>
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125294048</v>
+        <v>124258697</v>
       </c>
       <c r="B191" t="n">
-        <v>99118</v>
+        <v>57258</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Fluganvägen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>499093</v>
+        <v>498690</v>
       </c>
       <c r="R191" t="n">
-        <v>6909546</v>
+        <v>6910070</v>
       </c>
       <c r="S191" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -21241,12 +21226,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21255,75 +21240,71 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
-      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>125294065</v>
+        <v>124258627</v>
       </c>
       <c r="B192" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Fluganvägen, Mpd</t>
+          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>499078</v>
+        <v>498669</v>
       </c>
       <c r="R192" t="n">
-        <v>6909561</v>
+        <v>6909943</v>
       </c>
       <c r="S192" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21347,12 +21328,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21361,75 +21342,81 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>125294080</v>
+        <v>96765221</v>
       </c>
       <c r="B193" t="n">
-        <v>99118</v>
+        <v>57141</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Fluganvägen, Mpd</t>
+          <t>Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>499069</v>
+        <v>499049</v>
       </c>
       <c r="R193" t="n">
-        <v>6909556</v>
+        <v>6909619</v>
       </c>
       <c r="S193" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21453,12 +21440,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21467,72 +21454,73 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>125294113</v>
+        <v>124258047</v>
       </c>
       <c r="B194" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Fluganvägen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>499050</v>
+        <v>498617</v>
       </c>
       <c r="R194" t="n">
-        <v>6909565</v>
+        <v>6909667</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -21559,12 +21547,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21573,26 +21561,25 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
-      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>125294124</v>
+        <v>124257002</v>
       </c>
       <c r="B195" t="n">
         <v>99118</v>
@@ -21625,20 +21612,21 @@
           <t>50</t>
         </is>
       </c>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Fluganvägen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>499054</v>
+        <v>498588</v>
       </c>
       <c r="R195" t="n">
-        <v>6909570</v>
+        <v>6909664</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -21665,12 +21653,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21679,26 +21667,25 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>125294144</v>
+        <v>124257030</v>
       </c>
       <c r="B196" t="n">
         <v>99118</v>
@@ -21728,23 +21715,24 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Fluganvägen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>498894</v>
+        <v>498590</v>
       </c>
       <c r="R196" t="n">
-        <v>6909660</v>
+        <v>6909676</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -21771,12 +21759,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21785,26 +21773,25 @@
       <c r="AE196" t="b">
         <v>0</v>
       </c>
-      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>125294222</v>
+        <v>124257082</v>
       </c>
       <c r="B197" t="n">
         <v>99118</v>
@@ -21834,23 +21821,24 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Fluganvägen, Mpd</t>
+          <t>Nedre Butjärnen, Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>498858</v>
+        <v>498617</v>
       </c>
       <c r="R197" t="n">
-        <v>6909682</v>
+        <v>6909667</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -21877,12 +21865,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21891,26 +21879,25 @@
       <c r="AE197" t="b">
         <v>0</v>
       </c>
-      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>SCA SCA</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>125294252</v>
+        <v>125294144</v>
       </c>
       <c r="B198" t="n">
         <v>99118</v>
@@ -21940,7 +21927,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -21953,10 +21940,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>498853</v>
+        <v>498894</v>
       </c>
       <c r="R198" t="n">
-        <v>6909690</v>
+        <v>6909660</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -22016,7 +22003,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>125294362</v>
+        <v>125294222</v>
       </c>
       <c r="B199" t="n">
         <v>99118</v>
@@ -22046,7 +22033,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
@@ -22059,10 +22046,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>498585</v>
+        <v>498858</v>
       </c>
       <c r="R199" t="n">
-        <v>6909663</v>
+        <v>6909682</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -22122,7 +22109,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>125294386</v>
+        <v>125294252</v>
       </c>
       <c r="B200" t="n">
         <v>99118</v>
@@ -22152,7 +22139,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J200" t="inlineStr"/>
@@ -22165,10 +22152,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>498580</v>
+        <v>498853</v>
       </c>
       <c r="R200" t="n">
-        <v>6909673</v>
+        <v>6909690</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -22228,7 +22215,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>125294405</v>
+        <v>125294362</v>
       </c>
       <c r="B201" t="n">
         <v>99118</v>
@@ -22258,7 +22245,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J201" t="inlineStr"/>
@@ -22271,10 +22258,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>498579</v>
+        <v>498585</v>
       </c>
       <c r="R201" t="n">
-        <v>6909681</v>
+        <v>6909663</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -22334,7 +22321,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125294430</v>
+        <v>125294386</v>
       </c>
       <c r="B202" t="n">
         <v>99118</v>
@@ -22377,10 +22364,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>498567</v>
+        <v>498580</v>
       </c>
       <c r="R202" t="n">
-        <v>6909690</v>
+        <v>6909673</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -22440,7 +22427,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>125294451</v>
+        <v>125294405</v>
       </c>
       <c r="B203" t="n">
         <v>99118</v>
@@ -22470,7 +22457,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J203" t="inlineStr"/>
@@ -22483,10 +22470,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>498585</v>
+        <v>498579</v>
       </c>
       <c r="R203" t="n">
-        <v>6909699</v>
+        <v>6909681</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -22546,7 +22533,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>125294472</v>
+        <v>125294430</v>
       </c>
       <c r="B204" t="n">
         <v>99118</v>
@@ -22576,7 +22563,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J204" t="inlineStr"/>
@@ -22589,10 +22576,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>498591</v>
+        <v>498567</v>
       </c>
       <c r="R204" t="n">
-        <v>6909706</v>
+        <v>6909690</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -22652,48 +22639,56 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>124258697</v>
+        <v>125294451</v>
       </c>
       <c r="B205" t="n">
-        <v>57258</v>
+        <v>99118</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>100065</v>
+        <v>220787</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Fluganvägen, Mpd</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>498690</v>
+        <v>498585</v>
       </c>
       <c r="R205" t="n">
-        <v>6910070</v>
+        <v>6909699</v>
       </c>
       <c r="S205" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -22717,12 +22712,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22731,71 +22726,75 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
+      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>124258627</v>
+        <v>125294472</v>
       </c>
       <c r="B206" t="n">
-        <v>57953</v>
+        <v>99118</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Övre Butjärnen, Övre Butjärnen, Mpd</t>
+          <t>Fluganvägen, Mpd</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>498669</v>
+        <v>498591</v>
       </c>
       <c r="R206" t="n">
-        <v>6909943</v>
+        <v>6909706</v>
       </c>
       <c r="S206" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -22819,12 +22818,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22833,18 +22832,19 @@
       <c r="AE206" t="b">
         <v>0</v>
       </c>
+      <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>SCA SCA</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
@@ -23932,10 +23932,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>117700221</v>
+        <v>117700224</v>
       </c>
       <c r="B217" t="n">
-        <v>78993</v>
+        <v>78730</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23943,21 +23943,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23967,10 +23967,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>499088</v>
+        <v>499154</v>
       </c>
       <c r="R217" t="n">
-        <v>6912317</v>
+        <v>6912258</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24044,32 +24044,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>117700219</v>
+        <v>117700223</v>
       </c>
       <c r="B218" t="n">
-        <v>92083</v>
+        <v>79917</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24079,10 +24079,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>499055</v>
+        <v>499154</v>
       </c>
       <c r="R218" t="n">
-        <v>6912379</v>
+        <v>6912259</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24156,10 +24156,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>117700222</v>
+        <v>117700221</v>
       </c>
       <c r="B219" t="n">
-        <v>93197</v>
+        <v>78993</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24167,21 +24167,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -24194,7 +24194,7 @@
         <v>499088</v>
       </c>
       <c r="R219" t="n">
-        <v>6912315</v>
+        <v>6912317</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24268,32 +24268,32 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>117700224</v>
+        <v>117700236</v>
       </c>
       <c r="B220" t="n">
-        <v>78730</v>
+        <v>92557</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6437</v>
+        <v>483</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -24303,10 +24303,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>499154</v>
+        <v>499087</v>
       </c>
       <c r="R220" t="n">
-        <v>6912258</v>
+        <v>6912727</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24380,32 +24380,32 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>117700244</v>
+        <v>117700219</v>
       </c>
       <c r="B221" t="n">
-        <v>78730</v>
+        <v>92083</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -24415,10 +24415,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>498986</v>
+        <v>499055</v>
       </c>
       <c r="R221" t="n">
-        <v>6912503</v>
+        <v>6912379</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24492,10 +24492,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>117700241</v>
+        <v>117700238</v>
       </c>
       <c r="B222" t="n">
-        <v>79084</v>
+        <v>91962</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24503,21 +24503,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -24527,10 +24527,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>498988</v>
+        <v>499075</v>
       </c>
       <c r="R222" t="n">
-        <v>6912503</v>
+        <v>6912608</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24604,10 +24604,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>117700245</v>
+        <v>117700222</v>
       </c>
       <c r="B223" t="n">
-        <v>79946</v>
+        <v>93197</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24615,21 +24615,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -24639,10 +24639,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>498988</v>
+        <v>499088</v>
       </c>
       <c r="R223" t="n">
-        <v>6912489</v>
+        <v>6912315</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24716,10 +24716,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>117700243</v>
+        <v>117700244</v>
       </c>
       <c r="B224" t="n">
-        <v>78334</v>
+        <v>78730</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24727,21 +24727,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -24828,10 +24828,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>117700239</v>
+        <v>117700241</v>
       </c>
       <c r="B225" t="n">
-        <v>79085</v>
+        <v>79084</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24839,21 +24839,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -24863,10 +24863,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>498992</v>
+        <v>498988</v>
       </c>
       <c r="R225" t="n">
-        <v>6912533</v>
+        <v>6912503</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24940,10 +24940,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>117700246</v>
+        <v>117700237</v>
       </c>
       <c r="B226" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -24951,21 +24951,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -24975,10 +24975,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>498988</v>
+        <v>499065</v>
       </c>
       <c r="R226" t="n">
-        <v>6912489</v>
+        <v>6912628</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25052,10 +25052,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>117700247</v>
+        <v>117700245</v>
       </c>
       <c r="B227" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25063,21 +25063,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -25087,10 +25087,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>498975</v>
+        <v>498988</v>
       </c>
       <c r="R227" t="n">
-        <v>6912435</v>
+        <v>6912489</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25164,10 +25164,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>117700223</v>
+        <v>117700243</v>
       </c>
       <c r="B228" t="n">
-        <v>79917</v>
+        <v>78334</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25175,21 +25175,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -25199,10 +25199,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>499154</v>
+        <v>498986</v>
       </c>
       <c r="R228" t="n">
-        <v>6912259</v>
+        <v>6912503</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25276,10 +25276,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>117700242</v>
+        <v>117700239</v>
       </c>
       <c r="B229" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25287,21 +25287,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -25311,10 +25311,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>498988</v>
+        <v>498992</v>
       </c>
       <c r="R229" t="n">
-        <v>6912505</v>
+        <v>6912533</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25388,32 +25388,32 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>117700236</v>
+        <v>117700246</v>
       </c>
       <c r="B230" t="n">
-        <v>92557</v>
+        <v>79085</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>483</v>
+        <v>228912</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -25423,10 +25423,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>499087</v>
+        <v>498988</v>
       </c>
       <c r="R230" t="n">
-        <v>6912727</v>
+        <v>6912489</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25500,10 +25500,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>117700238</v>
+        <v>117700247</v>
       </c>
       <c r="B231" t="n">
-        <v>91962</v>
+        <v>79085</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25511,21 +25511,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -25535,10 +25535,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>499075</v>
+        <v>498975</v>
       </c>
       <c r="R231" t="n">
-        <v>6912608</v>
+        <v>6912435</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25612,10 +25612,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>117700237</v>
+        <v>117700242</v>
       </c>
       <c r="B232" t="n">
-        <v>79946</v>
+        <v>79917</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -25623,21 +25623,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -25647,10 +25647,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>499065</v>
+        <v>498988</v>
       </c>
       <c r="R232" t="n">
-        <v>6912628</v>
+        <v>6912505</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25823,7 +25823,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>96222534</v>
+        <v>99048889</v>
       </c>
       <c r="B234" t="n">
         <v>99118</v>
@@ -25852,18 +25852,20 @@
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Ånge, Mpd</t>
+          <t>Kroktjärnån 2, 700 m NO om Nedre Butjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>499352</v>
+        <v>499691</v>
       </c>
       <c r="R234" t="n">
-        <v>6910752</v>
+        <v>6910595</v>
       </c>
       <c r="S234" t="n">
         <v>25</v>
@@ -25888,14 +25890,19 @@
           <t>Haverö</t>
         </is>
       </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>Y-Ång-0133</t>
+        </is>
+      </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>2021-09-21</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2021-09-21</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -25904,6 +25911,7 @@
       <c r="AE234" t="b">
         <v>0</v>
       </c>
+      <c r="AF234" t="inlineStr"/>
       <c r="AG234" t="b">
         <v>0</v>
       </c>
@@ -25918,11 +25926,15 @@
           <t>Agneta Toomingas</t>
         </is>
       </c>
-      <c r="AY234" t="inlineStr"/>
+      <c r="AY234" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>99048889</v>
+        <v>96222534</v>
       </c>
       <c r="B235" t="n">
         <v>99118</v>
@@ -25951,20 +25963,18 @@
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Kroktjärnån 2, 700 m NO om Nedre Butjärnen, Mpd</t>
+          <t>Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>499691</v>
+        <v>499352</v>
       </c>
       <c r="R235" t="n">
-        <v>6910595</v>
+        <v>6910752</v>
       </c>
       <c r="S235" t="n">
         <v>25</v>
@@ -25989,19 +25999,14 @@
           <t>Haverö</t>
         </is>
       </c>
-      <c r="X235" t="inlineStr">
-        <is>
-          <t>Y-Ång-0133</t>
-        </is>
-      </c>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>2021-10-21</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -26010,7 +26015,6 @@
       <c r="AE235" t="b">
         <v>0</v>
       </c>
-      <c r="AF235" t="inlineStr"/>
       <c r="AG235" t="b">
         <v>0</v>
       </c>
@@ -26025,11 +26029,7 @@
           <t>Agneta Toomingas</t>
         </is>
       </c>
-      <c r="AY235" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
